--- a/svo_backend/valeurs_test.xlsx
+++ b/svo_backend/valeurs_test.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Men0_0\Desktop\Projet Angivy v2\test\Douane-export\svo_backend\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CA76C6-2D44-4816-A2D0-E72FB2E2FA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="645" windowWidth="19815" windowHeight="9915"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Valeurs" sheetId="1" r:id="rId1"/>
@@ -271,7 +277,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -312,6 +318,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -601,7 +610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -737,6 +746,9 @@
       <c r="U2" t="s">
         <v>36</v>
       </c>
+      <c r="W2">
+        <v>125</v>
+      </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -799,6 +811,9 @@
       <c r="U3" t="s">
         <v>46</v>
       </c>
+      <c r="W3">
+        <v>125</v>
+      </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -858,6 +873,9 @@
       <c r="U4" t="s">
         <v>57</v>
       </c>
+      <c r="W4">
+        <v>125</v>
+      </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -920,6 +938,9 @@
       <c r="U5" t="s">
         <v>69</v>
       </c>
+      <c r="W5">
+        <v>125</v>
+      </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -981,6 +1002,9 @@
       </c>
       <c r="U6" t="s">
         <v>78</v>
+      </c>
+      <c r="W6">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
